--- a/customer_profiles/shefish/templates/gs/pi.xlsx
+++ b/customer_profiles/shefish/templates/gs/pi.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="21600" windowHeight="10455" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="20475" windowHeight="5047" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -70,6 +70,18 @@
       <sz val="24"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <color rgb="FFFF0000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color rgb="FFFF0000"/>
+      <sz val="9"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
       <color rgb="FF00B0F0"/>
@@ -79,18 +91,6 @@
       <name val="Arial"/>
       <charset val="134"/>
       <b val="1"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <color rgb="FFFF0000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <color rgb="FFFF0000"/>
       <sz val="9"/>
     </font>
     <font>
@@ -1281,7 +1281,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="165">
+  <cellXfs count="146">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1337,6 +1337,16 @@
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0" hidden="0"/>
@@ -1345,7 +1355,7 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1374,7 +1384,7 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -1382,36 +1392,27 @@
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="89">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="87">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1425,7 +1426,7 @@
     <xf numFmtId="168" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="76">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="87">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="87">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1456,7 +1457,7 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="87">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="87">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="87">
@@ -1469,10 +1470,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="87">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="87">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="77">
@@ -1520,10 +1521,10 @@
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="57">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="57">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="57">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="57">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="57">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="99">
@@ -1573,11 +1574,21 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1606,7 +1617,7 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -1614,36 +1625,27 @@
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="89">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="87">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1685,10 +1687,10 @@
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="87">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="87">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="87">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="76">
@@ -1703,18 +1705,9 @@
     <xf numFmtId="168" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="87">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="167" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="169" fontId="1" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -1724,10 +1717,10 @@
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="57">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="57">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="57">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="57">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="57">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="99">
@@ -1763,50 +1756,6 @@
     </xf>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="87">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="117">
@@ -2235,7 +2184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="11.6"/>
   <cols>
     <col width="17.75" customWidth="1" style="6" min="1" max="1"/>
@@ -2291,371 +2240,398 @@
       <c r="G5" s="16" t="n"/>
       <c r="H5" s="16" t="n"/>
     </row>
-    <row r="6" ht="18" customFormat="1" customHeight="1" s="2">
-      <c r="A6" s="90" t="inlineStr">
+    <row r="6" ht="15.95" customFormat="1" customHeight="1" s="1">
+      <c r="A6" s="12" t="n"/>
+      <c r="B6" s="89" t="n"/>
+      <c r="E6" s="90" t="inlineStr">
+        <is>
+          <t>PI Number:</t>
+        </is>
+      </c>
+      <c r="F6" s="91" t="n"/>
+      <c r="G6" s="92" t="n"/>
+      <c r="H6" s="16" t="n"/>
+    </row>
+    <row r="7" ht="18" customFormat="1" customHeight="1" s="2">
+      <c r="A7" s="93" t="inlineStr">
         <is>
           <t>Incoterm:</t>
         </is>
       </c>
-      <c r="B6" s="160" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>DDP USA</t>
         </is>
       </c>
-      <c r="E6" s="93" t="inlineStr">
+      <c r="C7" s="94" t="n"/>
+      <c r="D7" s="95" t="n"/>
+      <c r="E7" s="96" t="inlineStr">
         <is>
           <t>PO Number:</t>
         </is>
       </c>
-      <c r="F6" s="94" t="n"/>
-      <c r="G6" s="115" t="n"/>
-      <c r="H6" s="115" t="n"/>
-    </row>
-    <row r="7" ht="18" customFormat="1" customHeight="1" s="2">
-      <c r="A7" s="90" t="inlineStr">
+      <c r="F7" s="97" t="n"/>
+      <c r="G7" s="94" t="n"/>
+    </row>
+    <row r="8" ht="18" customFormat="1" customHeight="1" s="2">
+      <c r="A8" s="93" t="inlineStr">
         <is>
           <t>Payment Terms:</t>
         </is>
       </c>
-      <c r="B7" s="160" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>Net 60 days</t>
         </is>
       </c>
-      <c r="E7" s="93" t="inlineStr">
+      <c r="C8" s="94" t="n"/>
+      <c r="D8" s="95" t="n"/>
+      <c r="E8" s="96" t="inlineStr">
         <is>
           <t>Document Date:</t>
         </is>
       </c>
-      <c r="F7" s="95" t="n"/>
-      <c r="G7" s="55" t="n"/>
-      <c r="H7" s="55" t="n"/>
-    </row>
-    <row r="8" ht="18" customFormat="1" customHeight="1" s="2">
-      <c r="A8" s="96" t="n"/>
-      <c r="B8" s="92" t="n"/>
-      <c r="C8" s="92" t="n"/>
-      <c r="D8" s="92" t="n"/>
-      <c r="E8" s="90" t="n"/>
-      <c r="F8" s="93" t="n"/>
-      <c r="G8" s="90" t="n"/>
-      <c r="H8" s="97" t="n"/>
-      <c r="I8" s="98" t="n"/>
+      <c r="F8" s="98" t="n"/>
+      <c r="G8" s="94" t="n"/>
     </row>
     <row r="9" ht="18" customFormat="1" customHeight="1" s="2">
-      <c r="A9" s="96" t="inlineStr">
+      <c r="A9" s="99" t="n"/>
+      <c r="B9" s="95" t="n"/>
+      <c r="C9" s="95" t="n"/>
+      <c r="D9" s="95" t="n"/>
+      <c r="E9" s="93" t="n"/>
+      <c r="F9" s="96" t="n"/>
+      <c r="G9" s="93" t="n"/>
+      <c r="H9" s="100" t="n"/>
+      <c r="I9" s="101" t="n"/>
+    </row>
+    <row r="10" ht="18" customFormat="1" customHeight="1" s="2">
+      <c r="A10" s="99" t="inlineStr">
         <is>
           <t>Bill To:</t>
         </is>
       </c>
-      <c r="B9" s="150" t="inlineStr">
+      <c r="B10" s="102" t="inlineStr">
         <is>
           <t>E MAX SPORT PTE. LTD.</t>
         </is>
       </c>
-      <c r="C9" s="151" t="n"/>
-      <c r="D9" s="151" t="n"/>
-      <c r="E9" s="101" t="inlineStr">
+      <c r="C10" s="103" t="n"/>
+      <c r="D10" s="94" t="n"/>
+      <c r="E10" s="104" t="inlineStr">
         <is>
           <t>Ship to:</t>
         </is>
       </c>
-      <c r="F9" s="152" t="inlineStr">
+      <c r="F10" s="102" t="inlineStr">
         <is>
           <t>E MAX SPORT PTE. LTD.</t>
         </is>
       </c>
-      <c r="G9" s="151" t="n"/>
-      <c r="H9" s="151" t="n"/>
-    </row>
-    <row r="10" ht="29" customFormat="1" customHeight="1" s="2">
-      <c r="A10" s="103" t="n"/>
-      <c r="B10" s="153" t="inlineStr">
-        <is>
-          <t>8 KAKI BUKIT AVENUE 4, #08-32,PREMIER @ KAKI BUKIT,</t>
-        </is>
-      </c>
-      <c r="C10" s="154" t="n"/>
-      <c r="D10" s="154" t="n"/>
-      <c r="E10" s="93" t="n"/>
-      <c r="F10" s="155" t="inlineStr">
-        <is>
-          <t>8 KAKI BUKIT AVENUE 4, #08-32,PREMIER @ KAKI BUKIT,</t>
-        </is>
-      </c>
-      <c r="G10" s="154" t="n"/>
-      <c r="H10" s="154" t="n"/>
+      <c r="G10" s="103" t="n"/>
+      <c r="H10" s="94" t="n"/>
     </row>
     <row r="11" ht="18" customFormat="1" customHeight="1" s="2">
-      <c r="A11" s="96" t="n"/>
-      <c r="B11" s="153" t="inlineStr">
+      <c r="A11" s="105" t="n"/>
+      <c r="B11" s="106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8 KAKI BUKIT AVENUE 4, </t>
+        </is>
+      </c>
+      <c r="C11" s="107" t="n"/>
+      <c r="D11" s="108" t="n"/>
+      <c r="E11" s="96" t="n"/>
+      <c r="F11" s="106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8 KAKI BUKIT AVENUE 4, </t>
+        </is>
+      </c>
+      <c r="G11" s="107" t="n"/>
+      <c r="H11" s="101" t="n"/>
+    </row>
+    <row r="12" ht="18" customFormat="1" customHeight="1" s="2">
+      <c r="A12" s="105" t="n"/>
+      <c r="B12" s="106" t="inlineStr">
+        <is>
+          <t>#08-32,PREMIER @ KAKI BUKIT,</t>
+        </is>
+      </c>
+      <c r="C12" s="107" t="n"/>
+      <c r="D12" s="108" t="n"/>
+      <c r="E12" s="96" t="n"/>
+      <c r="F12" s="106" t="inlineStr">
+        <is>
+          <t>#08-32,PREMIER @ KAKI BUKIT,</t>
+        </is>
+      </c>
+      <c r="G12" s="109" t="n"/>
+      <c r="H12" s="101" t="n"/>
+    </row>
+    <row r="13" ht="18" customFormat="1" customHeight="1" s="2">
+      <c r="A13" s="99" t="n"/>
+      <c r="B13" s="106" t="inlineStr">
         <is>
           <t>SINGAPORE 415875</t>
         </is>
       </c>
-      <c r="C11" s="154" t="n"/>
-      <c r="D11" s="154" t="n"/>
-      <c r="E11" s="108" t="n"/>
-      <c r="F11" s="156" t="inlineStr">
+      <c r="C13" s="107" t="n"/>
+      <c r="D13" s="108" t="n"/>
+      <c r="E13" s="110" t="n"/>
+      <c r="F13" s="106" t="inlineStr">
         <is>
           <t>SINGAPORE 415875</t>
         </is>
       </c>
-      <c r="G11" s="157" t="n"/>
-      <c r="H11" s="157" t="n"/>
-    </row>
-    <row r="12" ht="18" customFormat="1" customHeight="1" s="3">
-      <c r="A12" s="96" t="n"/>
-      <c r="B12" s="111" t="n"/>
-      <c r="C12" s="111" t="n"/>
-      <c r="D12" s="111" t="n"/>
-      <c r="E12" s="108" t="n"/>
-      <c r="F12" s="90" t="n"/>
-      <c r="G12" s="112" t="n"/>
-      <c r="H12" s="98" t="n"/>
-      <c r="L12" s="43" t="n"/>
-      <c r="M12" s="43" t="n"/>
-    </row>
-    <row r="13" ht="21.95" customFormat="1" customHeight="1" s="3">
-      <c r="A13" s="90" t="inlineStr">
+      <c r="G13" s="107" t="n"/>
+      <c r="H13" s="101" t="n"/>
+    </row>
+    <row r="14" ht="18" customFormat="1" customHeight="1" s="3">
+      <c r="A14" s="99" t="n"/>
+      <c r="B14" s="111" t="n"/>
+      <c r="C14" s="111" t="n"/>
+      <c r="D14" s="111" t="n"/>
+      <c r="E14" s="110" t="n"/>
+      <c r="F14" s="93" t="n"/>
+      <c r="G14" s="112" t="n"/>
+      <c r="H14" s="101" t="n"/>
+      <c r="L14" s="43" t="n"/>
+      <c r="M14" s="43" t="n"/>
+    </row>
+    <row r="15" ht="21.95" customFormat="1" customHeight="1" s="3">
+      <c r="A15" s="93" t="inlineStr">
         <is>
           <t>Port of Loading:</t>
         </is>
       </c>
-      <c r="B13" s="161" t="inlineStr">
+      <c r="B15" s="113" t="inlineStr">
         <is>
           <t>Qingdao, China</t>
         </is>
       </c>
-      <c r="E13" s="93" t="inlineStr">
+      <c r="C15" s="94" t="n"/>
+      <c r="D15" s="95" t="n"/>
+      <c r="E15" s="96" t="inlineStr">
         <is>
           <t>Actual Manufacturer Company Name</t>
         </is>
       </c>
-      <c r="F13" s="114" t="inlineStr">
+      <c r="F15" s="114" t="inlineStr">
         <is>
           <t>GLOBALSINO PTE.LTD.</t>
         </is>
       </c>
-      <c r="G13" s="115" t="n"/>
-      <c r="H13" s="115" t="n"/>
-      <c r="I13" s="91" t="n"/>
-      <c r="K13" s="43" t="n"/>
-      <c r="L13" s="43" t="n"/>
-      <c r="M13" s="43" t="n"/>
-    </row>
-    <row r="14" ht="29" customFormat="1" customHeight="1" s="3">
-      <c r="A14" s="90" t="inlineStr">
-        <is>
-          <t>Final Destination</t>
-        </is>
-      </c>
-      <c r="B14" s="162" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E14" s="93" t="inlineStr">
-        <is>
-          <t>Actual Manufacturer Company Address</t>
-        </is>
-      </c>
-      <c r="F14" s="114" t="inlineStr">
-        <is>
-          <t>10 KAKI BUKIT ROAD 2, #01-37, FIRST EAST CENTRE</t>
-        </is>
-      </c>
-      <c r="G14" s="115" t="n"/>
-      <c r="H14" s="115" t="n"/>
-      <c r="K14" s="43" t="n"/>
-      <c r="L14" s="52" t="n"/>
-      <c r="M14" s="52" t="n"/>
-    </row>
-    <row r="15" ht="21.95" customFormat="1" customHeight="1" s="3">
-      <c r="A15" s="96" t="n"/>
-      <c r="B15" s="111" t="n"/>
-      <c r="C15" s="111" t="n"/>
-      <c r="D15" s="111" t="n"/>
-      <c r="E15" s="120" t="n"/>
-      <c r="F15" s="121" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> SINGAPORE 417868</t>
-        </is>
-      </c>
-      <c r="G15" s="55" t="n"/>
-      <c r="H15" s="55" t="n"/>
-      <c r="K15" s="52" t="n"/>
+      <c r="G15" s="115" t="n"/>
+      <c r="H15" s="116" t="n"/>
+      <c r="I15" s="94" t="n"/>
+      <c r="K15" s="43" t="n"/>
       <c r="L15" s="43" t="n"/>
       <c r="M15" s="43" t="n"/>
     </row>
-    <row r="16" ht="7" customFormat="1" customHeight="1" s="122">
-      <c r="A16" s="123" t="n"/>
-      <c r="B16" s="124" t="n"/>
-      <c r="C16" s="124" t="n"/>
-      <c r="D16" s="124" t="n"/>
-      <c r="E16" s="124" t="n"/>
-      <c r="F16" s="124" t="n"/>
-      <c r="G16" s="124" t="n"/>
-      <c r="H16" s="124" t="n"/>
-    </row>
-    <row r="17" ht="24" customFormat="1" customHeight="1" s="122">
-      <c r="A17" s="58" t="inlineStr">
+    <row r="16" ht="21.95" customFormat="1" customHeight="1" s="3">
+      <c r="A16" s="93" t="inlineStr">
+        <is>
+          <t>Final Destination</t>
+        </is>
+      </c>
+      <c r="B16" s="117" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C16" s="94" t="n"/>
+      <c r="D16" s="111" t="n"/>
+      <c r="E16" s="96" t="inlineStr">
+        <is>
+          <t>Actual Manufacturer Company Address</t>
+        </is>
+      </c>
+      <c r="F16" s="118" t="inlineStr">
+        <is>
+          <t>10 KAKI BUKIT ROAD 2, #01-37, FIRST EAST CENTRE</t>
+        </is>
+      </c>
+      <c r="G16" s="118" t="n"/>
+      <c r="H16" s="119" t="n"/>
+      <c r="K16" s="43" t="n"/>
+      <c r="L16" s="52" t="n"/>
+      <c r="M16" s="52" t="n"/>
+    </row>
+    <row r="17" ht="21.95" customFormat="1" customHeight="1" s="3">
+      <c r="A17" s="99" t="n"/>
+      <c r="B17" s="111" t="n"/>
+      <c r="C17" s="111" t="n"/>
+      <c r="D17" s="111" t="n"/>
+      <c r="E17" s="120" t="n"/>
+      <c r="F17" s="121" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> SINGAPORE 417868</t>
+        </is>
+      </c>
+      <c r="G17" s="55" t="n"/>
+      <c r="H17" s="119" t="n"/>
+      <c r="K17" s="52" t="n"/>
+      <c r="L17" s="43" t="n"/>
+      <c r="M17" s="43" t="n"/>
+    </row>
+    <row r="18" ht="45" customFormat="1" customHeight="1" s="122">
+      <c r="A18" s="123" t="n"/>
+      <c r="B18" s="124" t="n"/>
+      <c r="C18" s="124" t="n"/>
+      <c r="D18" s="124" t="n"/>
+      <c r="E18" s="124" t="n"/>
+      <c r="F18" s="124" t="n"/>
+      <c r="G18" s="124" t="n"/>
+      <c r="H18" s="124" t="n"/>
+    </row>
+    <row r="19" ht="24" customFormat="1" customHeight="1" s="122">
+      <c r="A19" s="58" t="inlineStr">
         <is>
           <t>Country of The Origin</t>
         </is>
       </c>
-      <c r="B17" s="125" t="inlineStr">
+      <c r="B19" s="125" t="inlineStr">
         <is>
           <t>Item Number</t>
         </is>
       </c>
-      <c r="C17" s="125" t="inlineStr">
+      <c r="C19" s="125" t="inlineStr">
         <is>
           <t>UPC</t>
         </is>
       </c>
-      <c r="D17" s="60" t="inlineStr">
+      <c r="D19" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">Description </t>
         </is>
       </c>
-      <c r="E17" s="126" t="inlineStr">
+      <c r="E19" s="126" t="inlineStr">
         <is>
           <t>USD Unit Price</t>
         </is>
       </c>
-      <c r="F17" s="125" t="inlineStr">
+      <c r="F19" s="125" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="G17" s="127" t="inlineStr">
+      <c r="G19" s="127" t="inlineStr">
         <is>
           <t xml:space="preserve">USD Amount </t>
         </is>
       </c>
-      <c r="H17" s="128" t="inlineStr">
+      <c r="H19" s="128" t="inlineStr">
         <is>
           <t>EX-FACTORY DATE</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customFormat="1" customHeight="1" s="122">
-      <c r="A18" s="69" t="n"/>
-      <c r="B18" s="65" t="n"/>
-      <c r="C18" s="129" t="n"/>
-      <c r="D18" s="159" t="n"/>
-      <c r="E18" s="130" t="n"/>
-      <c r="F18" s="131" t="n"/>
-      <c r="G18" s="163" t="n"/>
-      <c r="H18" s="164" t="n"/>
-    </row>
-    <row r="19" ht="30" customFormat="1" customHeight="1" s="134">
-      <c r="A19" s="69" t="n"/>
-      <c r="B19" s="65" t="n"/>
-      <c r="C19" s="129" t="n"/>
-      <c r="D19" s="159" t="n"/>
-      <c r="E19" s="130" t="n"/>
-      <c r="F19" s="131" t="n"/>
-      <c r="G19" s="163" t="n"/>
-      <c r="H19" s="164" t="n"/>
-    </row>
-    <row r="20" ht="30" customFormat="1" customHeight="1" s="134">
-      <c r="A20" s="69" t="n"/>
+    <row r="20" ht="17.4" customFormat="1" customHeight="1" s="122">
+      <c r="A20" s="64" t="n"/>
       <c r="B20" s="65" t="n"/>
-      <c r="C20" s="129" t="n"/>
-      <c r="D20" s="159" t="n"/>
-      <c r="E20" s="130" t="n"/>
-      <c r="F20" s="131" t="n"/>
-      <c r="G20" s="163" t="n"/>
-      <c r="H20" s="164" t="n"/>
-    </row>
-    <row r="21" ht="30" customFormat="1" customHeight="1" s="134">
-      <c r="A21" s="69" t="n"/>
+      <c r="C20" s="66" t="n"/>
+      <c r="D20" s="67" t="n"/>
+      <c r="E20" s="129" t="n"/>
+      <c r="F20" s="69" t="n"/>
+      <c r="G20" s="70" t="n"/>
+      <c r="H20" s="130" t="n"/>
+    </row>
+    <row r="21" ht="17.4" customFormat="1" customHeight="1" s="131">
+      <c r="A21" s="64" t="n"/>
       <c r="B21" s="65" t="n"/>
-      <c r="C21" s="129" t="n"/>
-      <c r="D21" s="159" t="n"/>
-      <c r="E21" s="130" t="n"/>
-      <c r="F21" s="131" t="n"/>
-      <c r="G21" s="163" t="n"/>
-      <c r="H21" s="164" t="n"/>
-    </row>
-    <row r="22" ht="15.95" customFormat="1" customHeight="1" s="122">
-      <c r="A22" s="135" t="n"/>
-      <c r="B22" s="136" t="n"/>
-      <c r="C22" s="136" t="n"/>
-      <c r="D22" s="137" t="n"/>
-      <c r="E22" s="138" t="inlineStr">
+      <c r="C21" s="66" t="n"/>
+      <c r="D21" s="67" t="n"/>
+      <c r="E21" s="129" t="n"/>
+      <c r="F21" s="69" t="n"/>
+      <c r="G21" s="70" t="n"/>
+      <c r="H21" s="130" t="n"/>
+    </row>
+    <row r="22" ht="17.4" customFormat="1" customHeight="1" s="131">
+      <c r="A22" s="64" t="n"/>
+      <c r="B22" s="65" t="n"/>
+      <c r="C22" s="66" t="n"/>
+      <c r="D22" s="67" t="n"/>
+      <c r="E22" s="129" t="n"/>
+      <c r="F22" s="69" t="n"/>
+      <c r="G22" s="70" t="n"/>
+      <c r="H22" s="130" t="n"/>
+    </row>
+    <row r="23" ht="17.4" customFormat="1" customHeight="1" s="131">
+      <c r="A23" s="64" t="n"/>
+      <c r="B23" s="65" t="n"/>
+      <c r="C23" s="66" t="n"/>
+      <c r="D23" s="67" t="n"/>
+      <c r="E23" s="129" t="n"/>
+      <c r="F23" s="69" t="n"/>
+      <c r="G23" s="70" t="n"/>
+      <c r="H23" s="130" t="n"/>
+    </row>
+    <row r="24" ht="15.95" customFormat="1" customHeight="1" s="122">
+      <c r="A24" s="132" t="n"/>
+      <c r="B24" s="133" t="n"/>
+      <c r="C24" s="133" t="n"/>
+      <c r="D24" s="134" t="n"/>
+      <c r="E24" s="135" t="inlineStr">
         <is>
           <t xml:space="preserve">Sub-Total </t>
         </is>
       </c>
-      <c r="F22" s="76" t="n"/>
-      <c r="G22" s="77" t="n"/>
-      <c r="H22" s="139" t="n"/>
-    </row>
-    <row r="23" ht="15.95" customFormat="1" customHeight="1" s="134">
-      <c r="A23" s="140" t="n"/>
-      <c r="B23" s="140" t="n"/>
-      <c r="C23" s="140" t="n"/>
-      <c r="D23" s="140" t="n"/>
-      <c r="F23" s="141" t="inlineStr">
+      <c r="F24" s="76" t="n"/>
+      <c r="G24" s="77" t="n"/>
+      <c r="H24" s="136" t="n"/>
+    </row>
+    <row r="25" ht="15.95" customFormat="1" customHeight="1" s="131">
+      <c r="A25" s="137" t="n"/>
+      <c r="B25" s="137" t="n"/>
+      <c r="C25" s="137" t="n"/>
+      <c r="D25" s="137" t="n"/>
+      <c r="F25" s="138" t="inlineStr">
         <is>
           <t>TOTAL EXCLUDING EXCISE TAX  (USD)</t>
         </is>
       </c>
-      <c r="G23" s="81" t="n"/>
-      <c r="H23" s="142" t="n"/>
-    </row>
-    <row r="24" ht="15.95" customFormat="1" customHeight="1" s="134">
-      <c r="H24" s="142" t="n"/>
-    </row>
-    <row r="25" ht="15.95" customFormat="1" customHeight="1" s="134">
-      <c r="A25" s="143" t="n"/>
-      <c r="E25" s="144" t="inlineStr">
+      <c r="G25" s="81" t="n"/>
+      <c r="H25" s="139" t="n"/>
+    </row>
+    <row r="26" ht="15.95" customFormat="1" customHeight="1" s="131">
+      <c r="H26" s="139" t="n"/>
+    </row>
+    <row r="27" ht="15.95" customFormat="1" customHeight="1" s="131">
+      <c r="A27" s="140" t="n"/>
+      <c r="E27" s="141" t="inlineStr">
         <is>
           <t>Signature:</t>
         </is>
       </c>
-      <c r="F25" s="145" t="n"/>
-      <c r="G25" s="145" t="n"/>
-      <c r="H25" s="91" t="n"/>
-    </row>
-    <row r="26" ht="15.95" customFormat="1" customHeight="1" s="134">
-      <c r="A26" s="143" t="n"/>
-      <c r="E26" s="146" t="inlineStr">
+      <c r="F27" s="142" t="n"/>
+      <c r="G27" s="142" t="n"/>
+      <c r="H27" s="94" t="n"/>
+    </row>
+    <row r="28" ht="15.95" customFormat="1" customHeight="1" s="131">
+      <c r="A28" s="140" t="n"/>
+      <c r="E28" s="143" t="inlineStr">
         <is>
           <t>Date:</t>
         </is>
       </c>
-      <c r="F26" s="147" t="n"/>
-      <c r="G26" s="148" t="n"/>
-      <c r="H26" s="91" t="n"/>
+      <c r="F28" s="144" t="n"/>
+      <c r="G28" s="145" t="n"/>
+      <c r="H28" s="94" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="F10:H10"/>
+  <mergeCells count="5">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="F13:H13"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="F15:G15"/>
     <mergeCell ref="A2:D3"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="F17:G17"/>
     <mergeCell ref="E1:H4"/>
   </mergeCells>
-  <conditionalFormatting sqref="B18">
+  <conditionalFormatting sqref="B20">
+    <cfRule type="duplicateValues" priority="3" dxfId="0"/>
     <cfRule type="duplicateValues" priority="4" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="3" dxfId="0"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B19:B21">
+  <conditionalFormatting sqref="B21:B23">
+    <cfRule type="duplicateValues" priority="1" dxfId="0"/>
     <cfRule type="duplicateValues" priority="2" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="1" dxfId="0"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" scale="58"/>
